--- a/Rao_diversity1.xlsx
+++ b/Rao_diversity1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dominik\Cesky_Hradek\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stoces\Documents\Cesky_Hradek\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95887E3A-5F4B-4B30-A047-8B598101511D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C38B7F-E5F8-4F20-9ECC-13BA6A8764A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="traits" sheetId="1" r:id="rId1"/>
@@ -36,20 +36,20 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
   <si>
     <t>Species</t>
-  </si>
-  <si>
-    <t>Body size</t>
   </si>
   <si>
     <t>Trophic</t>
@@ -342,6 +342,18 @@
   <si>
     <t>Q</t>
   </si>
+  <si>
+    <t>Bioindication.group</t>
+  </si>
+  <si>
+    <t>Moisture.tolerance</t>
+  </si>
+  <si>
+    <t>Areal.distribution</t>
+  </si>
+  <si>
+    <t>Body.size</t>
+  </si>
 </sst>
 </file>
 
@@ -381,7 +393,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -389,11 +401,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -407,6 +439,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -689,29 +727,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CO88"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="8.85546875"/>
+    <col min="5" max="5" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:93" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:93" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="B2" s="1">
         <v>3</v>
@@ -722,10 +771,19 @@
       <c r="D2" s="1">
         <v>18.600000000000001</v>
       </c>
+      <c r="E2" s="1">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1">
         <v>3</v>
@@ -736,7 +794,15 @@
       <c r="D3" s="1">
         <v>15.1</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="E3" s="1">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>4</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -824,9 +890,9 @@
       <c r="CN3" s="2"/>
       <c r="CO3" s="2"/>
     </row>
-    <row r="4" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -837,10 +903,19 @@
       <c r="D4" s="1">
         <v>8.6999999999999993</v>
       </c>
+      <c r="E4" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>5</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -851,10 +926,19 @@
       <c r="D5" s="1">
         <v>7.5</v>
       </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="6" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -865,10 +949,19 @@
       <c r="D6" s="1">
         <v>12.5</v>
       </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="7" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -879,10 +972,19 @@
       <c r="D7" s="1">
         <v>7.5</v>
       </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -893,10 +995,19 @@
       <c r="D8" s="1">
         <v>7.7</v>
       </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -907,10 +1018,19 @@
       <c r="D9" s="3">
         <v>6.6</v>
       </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
@@ -921,10 +1041,19 @@
       <c r="D10" s="1">
         <v>11</v>
       </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
@@ -935,10 +1064,19 @@
       <c r="D11" s="1">
         <v>7.8</v>
       </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>4</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
@@ -949,10 +1087,19 @@
       <c r="D12" s="1">
         <v>6.5</v>
       </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
@@ -963,10 +1110,19 @@
       <c r="D13" s="1">
         <v>7.7</v>
       </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="14" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -977,10 +1133,19 @@
       <c r="D14" s="1">
         <v>7.5</v>
       </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>3</v>
+      </c>
+      <c r="G14" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
@@ -991,10 +1156,19 @@
       <c r="D15" s="1">
         <v>7.4</v>
       </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>3</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
@@ -1005,10 +1179,19 @@
       <c r="D16" s="3">
         <v>9</v>
       </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
@@ -1019,10 +1202,19 @@
       <c r="D17" s="1">
         <v>8.8000000000000007</v>
       </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>3</v>
+      </c>
+      <c r="G17" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
@@ -1033,10 +1225,19 @@
       <c r="D18" s="1">
         <v>6.8</v>
       </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
@@ -1047,10 +1248,19 @@
       <c r="D19" s="1">
         <v>4.4000000000000004</v>
       </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>4</v>
+      </c>
+      <c r="G19" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="1">
         <v>3</v>
@@ -1061,10 +1271,19 @@
       <c r="D20" s="1">
         <v>6.6</v>
       </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5</v>
+      </c>
+      <c r="G20" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
@@ -1075,10 +1294,19 @@
       <c r="D21" s="3">
         <v>4</v>
       </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1">
+        <v>4</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1">
         <v>2</v>
@@ -1089,10 +1317,19 @@
       <c r="D22" s="1">
         <v>3.3</v>
       </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="1">
         <v>3</v>
@@ -1103,10 +1340,19 @@
       <c r="D23" s="1">
         <v>3.5</v>
       </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
@@ -1117,10 +1363,19 @@
       <c r="D24" s="1">
         <v>3.7</v>
       </c>
+      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+      <c r="F24" s="1">
+        <v>4</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="1">
         <v>2</v>
@@ -1131,10 +1386,19 @@
       <c r="D25" s="1">
         <v>4.0999999999999996</v>
       </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>4</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" s="1">
         <v>2</v>
@@ -1145,10 +1409,19 @@
       <c r="D26" s="1">
         <v>4.3</v>
       </c>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="1">
         <v>2</v>
@@ -1159,10 +1432,19 @@
       <c r="D27" s="1">
         <v>4.7</v>
       </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1">
+        <v>2</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="1">
         <v>2</v>
@@ -1173,10 +1455,19 @@
       <c r="D28" s="1">
         <v>11.5</v>
       </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>2</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="1">
         <v>3</v>
@@ -1187,10 +1478,19 @@
       <c r="D29" s="1">
         <v>7.9</v>
       </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1">
+        <v>4</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="1">
         <v>3</v>
@@ -1201,10 +1501,19 @@
       <c r="D30" s="1">
         <v>18</v>
       </c>
+      <c r="E30" s="1">
+        <v>2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>4</v>
+      </c>
+      <c r="G30" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="1">
         <v>3</v>
@@ -1215,10 +1524,19 @@
       <c r="D31" s="1">
         <v>22</v>
       </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+      <c r="F31" s="1">
+        <v>4</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="1">
         <v>3</v>
@@ -1229,10 +1547,19 @@
       <c r="D32" s="1">
         <v>23.5</v>
       </c>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
+      <c r="F32" s="1">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" s="1">
         <v>3</v>
@@ -1243,10 +1570,19 @@
       <c r="D33" s="3">
         <v>17</v>
       </c>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+      <c r="F33" s="1">
+        <v>3</v>
+      </c>
+      <c r="G33" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" s="1">
         <v>3</v>
@@ -1257,10 +1593,19 @@
       <c r="D34" s="1">
         <v>23.5</v>
       </c>
+      <c r="E34" s="1">
+        <v>2</v>
+      </c>
+      <c r="F34" s="1">
+        <v>2</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="1">
         <v>3</v>
@@ -1271,10 +1616,19 @@
       <c r="D35" s="1">
         <v>35</v>
       </c>
+      <c r="E35" s="1">
+        <v>2</v>
+      </c>
+      <c r="F35" s="1">
+        <v>3</v>
+      </c>
+      <c r="G35" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="1">
         <v>3</v>
@@ -1285,10 +1639,19 @@
       <c r="D36" s="1">
         <v>25</v>
       </c>
+      <c r="E36" s="1">
+        <v>2</v>
+      </c>
+      <c r="F36" s="1">
+        <v>4</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="1">
         <v>3</v>
@@ -1299,10 +1662,19 @@
       <c r="D37" s="1">
         <v>28</v>
       </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="F37" s="1">
+        <v>4</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="1">
         <v>3</v>
@@ -1313,10 +1685,19 @@
       <c r="D38" s="1">
         <v>24</v>
       </c>
+      <c r="E38" s="1">
+        <v>2</v>
+      </c>
+      <c r="F38" s="1">
+        <v>4</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="1">
         <v>3</v>
@@ -1327,10 +1708,19 @@
       <c r="D39" s="1">
         <v>23.5</v>
       </c>
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+      <c r="F39" s="1">
+        <v>3</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="1">
         <v>3</v>
@@ -1341,10 +1731,19 @@
       <c r="D40" s="1">
         <v>24</v>
       </c>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+      <c r="F40" s="1">
+        <v>4</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" s="1">
         <v>3</v>
@@ -1355,10 +1754,19 @@
       <c r="D41" s="1">
         <v>21</v>
       </c>
+      <c r="E41" s="1">
+        <v>2</v>
+      </c>
+      <c r="F41" s="1">
+        <v>4</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="1">
         <v>3</v>
@@ -1369,10 +1777,19 @@
       <c r="D42" s="1">
         <v>28.5</v>
       </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="F42" s="1">
+        <v>3</v>
+      </c>
+      <c r="G42" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" s="1">
         <v>3</v>
@@ -1383,10 +1800,19 @@
       <c r="D43" s="1">
         <v>13.5</v>
       </c>
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" s="1">
         <v>3</v>
@@ -1397,10 +1823,19 @@
       <c r="D44" s="1">
         <v>5</v>
       </c>
+      <c r="E44" s="1">
+        <v>3</v>
+      </c>
+      <c r="F44" s="1">
+        <v>4</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" s="1">
         <v>3</v>
@@ -1411,10 +1846,19 @@
       <c r="D45" s="1">
         <v>18</v>
       </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+      <c r="F45" s="1">
+        <v>4</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" s="1">
         <v>3</v>
@@ -1425,10 +1869,19 @@
       <c r="D46" s="1">
         <v>4.3</v>
       </c>
+      <c r="E46" s="1">
+        <v>2</v>
+      </c>
+      <c r="F46" s="1">
+        <v>5</v>
+      </c>
+      <c r="G46" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" s="1">
         <v>3</v>
@@ -1439,10 +1892,19 @@
       <c r="D47" s="1">
         <v>5.6</v>
       </c>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
+      <c r="F47" s="1">
+        <v>3</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" s="1">
         <v>3</v>
@@ -1453,10 +1915,19 @@
       <c r="D48" s="1">
         <v>2.5</v>
       </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1">
+        <v>5</v>
+      </c>
+      <c r="G48" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" s="1">
         <v>3</v>
@@ -1467,10 +1938,19 @@
       <c r="D49" s="1">
         <v>3.9</v>
       </c>
+      <c r="E49" s="1">
+        <v>2</v>
+      </c>
+      <c r="F49" s="1">
+        <v>5</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" s="1">
         <v>3</v>
@@ -1481,10 +1961,19 @@
       <c r="D50" s="1">
         <v>6.5</v>
       </c>
+      <c r="E50" s="1">
+        <v>2</v>
+      </c>
+      <c r="F50" s="1">
+        <v>5</v>
+      </c>
+      <c r="G50" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" s="1">
         <v>3</v>
@@ -1495,10 +1984,19 @@
       <c r="D51" s="1">
         <v>6.7</v>
       </c>
+      <c r="E51" s="1">
+        <v>2</v>
+      </c>
+      <c r="F51" s="1">
+        <v>5</v>
+      </c>
+      <c r="G51" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" s="1">
         <v>2</v>
@@ -1509,10 +2007,19 @@
       <c r="D52" s="1">
         <v>10.199999999999999</v>
       </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1">
+        <v>3</v>
+      </c>
+      <c r="G52" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" s="1">
         <v>2</v>
@@ -1523,10 +2030,19 @@
       <c r="D53" s="1">
         <v>9.6999999999999993</v>
       </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1">
+        <v>3</v>
+      </c>
+      <c r="G53" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" s="1">
         <v>1</v>
@@ -1537,10 +2053,19 @@
       <c r="D54" s="1">
         <v>9.3000000000000007</v>
       </c>
+      <c r="E54" s="1">
+        <v>2</v>
+      </c>
+      <c r="F54" s="1">
+        <v>3</v>
+      </c>
+      <c r="G54" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" s="1">
         <v>2</v>
@@ -1551,10 +2076,19 @@
       <c r="D55" s="1">
         <v>7.5</v>
       </c>
+      <c r="E55" s="1">
+        <v>2</v>
+      </c>
+      <c r="F55" s="1">
+        <v>3</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" s="1">
         <v>1</v>
@@ -1565,10 +2099,19 @@
       <c r="D56" s="1">
         <v>10.5</v>
       </c>
+      <c r="E56" s="1">
+        <v>2</v>
+      </c>
+      <c r="F56" s="1">
+        <v>3</v>
+      </c>
+      <c r="G56" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" s="1">
         <v>2</v>
@@ -1579,10 +2122,19 @@
       <c r="D57" s="1">
         <v>9.9</v>
       </c>
+      <c r="E57" s="1">
+        <v>2</v>
+      </c>
+      <c r="F57" s="1">
+        <v>2</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" s="1">
         <v>3</v>
@@ -1593,10 +2145,19 @@
       <c r="D58" s="1">
         <v>6.9</v>
       </c>
+      <c r="E58" s="1">
+        <v>2</v>
+      </c>
+      <c r="F58" s="1">
+        <v>4</v>
+      </c>
+      <c r="G58" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" s="1">
         <v>3</v>
@@ -1607,10 +2168,19 @@
       <c r="D59" s="1">
         <v>7.4</v>
       </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="1">
+        <v>3</v>
+      </c>
+      <c r="G59" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" s="1">
         <v>3</v>
@@ -1621,10 +2191,19 @@
       <c r="D60" s="1">
         <v>2.6</v>
       </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1">
+        <v>2</v>
+      </c>
+      <c r="G60" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" s="1">
         <v>3</v>
@@ -1635,10 +2214,19 @@
       <c r="D61" s="1">
         <v>15.8</v>
       </c>
+      <c r="E61" s="1">
+        <v>2</v>
+      </c>
+      <c r="F61" s="1">
+        <v>2</v>
+      </c>
+      <c r="G61" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" s="1">
         <v>3</v>
@@ -1649,10 +2237,19 @@
       <c r="D62" s="1">
         <v>11.5</v>
       </c>
+      <c r="E62" s="1">
+        <v>2</v>
+      </c>
+      <c r="F62" s="1">
+        <v>3</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" s="1">
         <v>3</v>
@@ -1663,10 +2260,19 @@
       <c r="D63" s="3">
         <v>5</v>
       </c>
+      <c r="E63" s="1">
+        <v>2</v>
+      </c>
+      <c r="F63" s="1">
+        <v>3</v>
+      </c>
+      <c r="G63" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" s="1">
         <v>3</v>
@@ -1677,10 +2283,19 @@
       <c r="D64" s="1">
         <v>5.8</v>
       </c>
+      <c r="E64" s="1">
+        <v>2</v>
+      </c>
+      <c r="F64" s="1">
+        <v>3</v>
+      </c>
+      <c r="G64" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" s="1">
         <v>3</v>
@@ -1691,10 +2306,19 @@
       <c r="D65" s="1">
         <v>4.3</v>
       </c>
+      <c r="E65" s="1">
+        <v>2</v>
+      </c>
+      <c r="F65" s="1">
+        <v>3</v>
+      </c>
+      <c r="G65" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" s="1">
         <v>3</v>
@@ -1705,10 +2329,19 @@
       <c r="D66" s="1">
         <v>4.5</v>
       </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="1">
+        <v>3</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" s="1">
         <v>1</v>
@@ -1719,10 +2352,19 @@
       <c r="D67" s="1">
         <v>11.5</v>
       </c>
+      <c r="E67" s="1">
+        <v>2</v>
+      </c>
+      <c r="F67" s="1">
+        <v>4</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" s="1">
         <v>2</v>
@@ -1733,10 +2375,19 @@
       <c r="D68" s="1">
         <v>7.6</v>
       </c>
+      <c r="E68" s="1">
+        <v>2</v>
+      </c>
+      <c r="F68" s="1">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" s="1">
         <v>3</v>
@@ -1747,10 +2398,19 @@
       <c r="D69" s="1">
         <v>3.2</v>
       </c>
+      <c r="E69" s="1">
+        <v>2</v>
+      </c>
+      <c r="F69" s="1">
+        <v>3</v>
+      </c>
+      <c r="G69" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" s="1">
         <v>2</v>
@@ -1761,10 +2421,19 @@
       <c r="D70" s="1">
         <v>12.1</v>
       </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1">
+        <v>3</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" s="1">
         <v>3</v>
@@ -1775,10 +2444,19 @@
       <c r="D71" s="1">
         <v>10.7</v>
       </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1">
+        <v>3</v>
+      </c>
+      <c r="G71" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" s="1">
         <v>2</v>
@@ -1789,10 +2467,19 @@
       <c r="D72" s="1">
         <v>13.8</v>
       </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="1">
+        <v>3</v>
+      </c>
+      <c r="G72" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" s="1">
         <v>3</v>
@@ -1803,10 +2490,19 @@
       <c r="D73" s="1">
         <v>11</v>
       </c>
+      <c r="E73" s="1">
+        <v>2</v>
+      </c>
+      <c r="F73" s="1">
+        <v>4</v>
+      </c>
+      <c r="G73" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" s="1">
         <v>3</v>
@@ -1817,10 +2513,19 @@
       <c r="D74" s="1">
         <v>13.5</v>
       </c>
+      <c r="E74" s="1">
+        <v>2</v>
+      </c>
+      <c r="F74" s="1">
+        <v>4</v>
+      </c>
+      <c r="G74" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" s="1">
         <v>3</v>
@@ -1831,10 +2536,19 @@
       <c r="D75" s="3">
         <v>10</v>
       </c>
+      <c r="E75" s="1">
+        <v>2</v>
+      </c>
+      <c r="F75" s="1">
+        <v>5</v>
+      </c>
+      <c r="G75" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" s="1">
         <v>2</v>
@@ -1845,10 +2559,19 @@
       <c r="D76" s="3">
         <v>15</v>
       </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="1">
+        <v>3</v>
+      </c>
+      <c r="G76" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" s="1">
         <v>3</v>
@@ -1859,10 +2582,19 @@
       <c r="D77" s="1">
         <v>18.5</v>
       </c>
+      <c r="E77" s="1">
+        <v>2</v>
+      </c>
+      <c r="F77" s="1">
+        <v>4</v>
+      </c>
+      <c r="G77" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" s="1">
         <v>3</v>
@@ -1873,10 +2605,19 @@
       <c r="D78" s="3">
         <v>11</v>
       </c>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="1">
+        <v>5</v>
+      </c>
+      <c r="G78" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" s="1">
         <v>3</v>
@@ -1887,10 +2628,19 @@
       <c r="D79" s="1">
         <v>11.4</v>
       </c>
+      <c r="E79" s="1">
+        <v>2</v>
+      </c>
+      <c r="F79" s="1">
+        <v>4</v>
+      </c>
+      <c r="G79" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" s="1">
         <v>3</v>
@@ -1901,10 +2651,19 @@
       <c r="D80" s="1">
         <v>9.6</v>
       </c>
+      <c r="E80" s="1">
+        <v>2</v>
+      </c>
+      <c r="F80" s="1">
+        <v>5</v>
+      </c>
+      <c r="G80" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" s="1">
         <v>2</v>
@@ -1915,10 +2674,19 @@
       <c r="D81" s="3">
         <v>6</v>
       </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="1">
+        <v>4</v>
+      </c>
+      <c r="G81" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" s="1">
         <v>3</v>
@@ -1929,10 +2697,19 @@
       <c r="D82" s="1">
         <v>2.8</v>
       </c>
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="1">
+        <v>2</v>
+      </c>
+      <c r="G82" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" s="1">
         <v>2</v>
@@ -1943,10 +2720,19 @@
       <c r="D83" s="1">
         <v>5.8</v>
       </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1">
+        <v>3</v>
+      </c>
+      <c r="G83" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" s="1">
         <v>3</v>
@@ -1957,10 +2743,19 @@
       <c r="D84" s="1">
         <v>3.8</v>
       </c>
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+      <c r="F84" s="1">
+        <v>3</v>
+      </c>
+      <c r="G84" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" s="1">
         <v>3</v>
@@ -1971,10 +2766,19 @@
       <c r="D85" s="1">
         <v>5.5</v>
       </c>
+      <c r="E85" s="1">
+        <v>2</v>
+      </c>
+      <c r="F85" s="1">
+        <v>5</v>
+      </c>
+      <c r="G85" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" s="1">
         <v>3</v>
@@ -1985,10 +2789,19 @@
       <c r="D86" s="1">
         <v>3.5</v>
       </c>
+      <c r="E86" s="1">
+        <v>2</v>
+      </c>
+      <c r="F86" s="1">
+        <v>4</v>
+      </c>
+      <c r="G86" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" s="1">
         <v>3</v>
@@ -1999,10 +2812,19 @@
       <c r="D87" s="1">
         <v>4.8</v>
       </c>
+      <c r="E87" s="1">
+        <v>2</v>
+      </c>
+      <c r="F87" s="1">
+        <v>5</v>
+      </c>
+      <c r="G87" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B88" s="1">
         <v>3</v>
@@ -2012,6 +2834,15 @@
       </c>
       <c r="D88" s="1">
         <v>7.6</v>
+      </c>
+      <c r="E88" s="7">
+        <v>2</v>
+      </c>
+      <c r="F88" s="7">
+        <v>3</v>
+      </c>
+      <c r="G88" s="7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2023,275 +2854,275 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AD83D82-658B-43C3-8E41-1433D4E4F72D}">
   <dimension ref="A1:CJ306"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AS1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AT1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AU1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AV1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AW1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AX1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AY1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BA1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BB1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BC1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BD1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BE1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BF1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BG1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BH1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BI1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BJ1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BK1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BL1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BM1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BN1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BO1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BP1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BR1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BS1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BT1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BU1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BV1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BW1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BX1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BY1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BZ1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="CA1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="CB1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="CC1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CD1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CE1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CF1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CG1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CH1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CI1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="CJ1" s="2" t="s">
-        <v>91</v>
-      </c>
     </row>
-    <row r="2" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2557,7 +3388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2823,7 +3654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3089,7 +3920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3355,7 +4186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3621,7 +4452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3887,7 +4718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4153,7 +4984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4419,7 +5250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4685,7 +5516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4951,7 +5782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5217,7 +6048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5483,7 +6314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5749,7 +6580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6015,7 +6846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6281,7 +7112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6547,7 +7378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6813,7 +7644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -7079,7 +7910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -7345,7 +8176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -7611,7 +8442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7877,7 +8708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -8143,7 +8974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -8409,7 +9240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -8675,7 +9506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -8941,7 +9772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -9207,7 +10038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -9473,7 +10304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -9739,7 +10570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -10005,7 +10836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -10271,7 +11102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -10537,7 +11368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -10803,7 +11634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -11069,7 +11900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -11335,7 +12166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -11601,7 +12432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -11867,7 +12698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -12133,7 +12964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -12399,7 +13230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -12665,7 +13496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -12931,7 +13762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -13197,7 +14028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -13463,7 +14294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -13729,7 +14560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -13995,7 +14826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -14261,7 +15092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -14527,7 +15358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -14793,7 +15624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -15059,7 +15890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -15325,7 +16156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -15591,7 +16422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -15857,7 +16688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -16123,7 +16954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -16389,7 +17220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -16655,7 +17486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -16921,7 +17752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -17187,7 +18018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -17453,7 +18284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -17719,7 +18550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -17985,7 +18816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -18251,7 +19082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -18517,7 +19348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -18783,7 +19614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -19049,7 +19880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -19315,7 +20146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -19581,7 +20412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -19847,7 +20678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -20113,7 +20944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -20379,7 +21210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -20645,7 +21476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -20911,7 +21742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -21177,7 +22008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -21443,7 +22274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -21709,7 +22540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -21975,7 +22806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -22241,7 +23072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -22507,7 +23338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -22773,7 +23604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -23039,7 +23870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -23305,7 +24136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -23571,7 +24402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -23837,7 +24668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -24103,7 +24934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -24369,7 +25200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -24635,7 +25466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -24901,7 +25732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -25167,7 +25998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -25433,7 +26264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -25699,7 +26530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -25965,7 +26796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -26231,7 +27062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -26497,7 +27328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -26763,7 +27594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -27029,7 +27860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -27295,7 +28126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -27561,7 +28392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -27827,7 +28658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -28093,7 +28924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -28359,7 +29190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -28625,7 +29456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -28891,7 +29722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -29157,7 +29988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -29423,7 +30254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -29689,7 +30520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -29955,7 +30786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -30221,7 +31052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -30487,7 +31318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -30753,7 +31584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -31019,7 +31850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -31285,7 +32116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -31551,7 +32382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -31817,7 +32648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -32083,7 +32914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -32349,7 +33180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -32615,7 +33446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -32881,7 +33712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -33147,7 +33978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -33413,7 +34244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -33679,7 +34510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -33945,7 +34776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -34211,7 +35042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -34477,7 +35308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -34743,7 +35574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -35009,7 +35840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -35275,7 +36106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -35541,7 +36372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -35807,7 +36638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -36073,7 +36904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -36339,7 +37170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -36605,7 +37436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -36871,7 +37702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -37137,7 +37968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -37403,7 +38234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -37669,7 +38500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -37935,7 +38766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -38201,7 +39032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -38467,7 +39298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -38733,7 +39564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -38999,7 +39830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -39265,7 +40096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -39531,7 +40362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -39797,7 +40628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -40063,7 +40894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -40329,7 +41160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -40595,7 +41426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -40861,7 +41692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -41127,7 +41958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -41393,7 +42224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -41659,7 +42490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -41925,7 +42756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -42191,7 +43022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -42457,7 +43288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -42723,7 +43554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -42989,7 +43820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -43255,7 +44086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -43521,7 +44352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -43787,7 +44618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -44053,7 +44884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -44319,7 +45150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -44585,7 +45416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -44851,7 +45682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -45117,7 +45948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -45383,7 +46214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -45649,7 +46480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -45915,7 +46746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -46181,7 +47012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -46447,7 +47278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -46713,7 +47544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -46979,7 +47810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -47245,7 +48076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -47511,7 +48342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -47777,7 +48608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -48043,7 +48874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -48309,7 +49140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -48575,7 +49406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -48841,7 +49672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -49107,7 +49938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -49373,7 +50204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -49639,7 +50470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -49905,7 +50736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -50171,7 +51002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -50437,7 +51268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -50703,7 +51534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -50969,7 +51800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -51235,7 +52066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -51501,7 +52332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -51767,7 +52598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -52033,7 +52864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -52299,7 +53130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -52565,7 +53396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -52831,7 +53662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -53097,7 +53928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -53363,7 +54194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -53629,7 +54460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -53895,7 +54726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -54161,7 +54992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -54427,7 +55258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -54693,7 +55524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -54959,7 +55790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -55225,7 +56056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -55491,7 +56322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -55757,7 +56588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -56023,7 +56854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -56289,7 +57120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -56555,7 +57386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -56821,7 +57652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -57087,7 +57918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -57353,7 +58184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -57619,7 +58450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -57885,7 +58716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -58151,7 +58982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -58417,7 +59248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -58683,7 +59514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -58949,7 +59780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -59215,7 +60046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -59481,7 +60312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -59747,7 +60578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -60013,7 +60844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -60279,7 +61110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -60545,7 +61376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -60811,7 +61642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -61077,7 +61908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -61343,7 +62174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -61609,7 +62440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -61875,7 +62706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -62141,7 +62972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -62407,7 +63238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -62673,7 +63504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -62939,7 +63770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -63205,7 +64036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -63471,7 +64302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -63737,7 +64568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -64003,7 +64834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -64269,7 +65100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -64535,7 +65366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -64801,7 +65632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -65067,7 +65898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -65333,7 +66164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -65599,7 +66430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -65865,7 +66696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -66131,7 +66962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -66397,7 +67228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -66663,7 +67494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -66929,7 +67760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -67195,7 +68026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -67461,7 +68292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -67727,7 +68558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -67993,7 +68824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -68259,7 +69090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>249</v>
       </c>
@@ -68525,7 +69356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -68791,7 +69622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -69057,7 +69888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -69323,7 +70154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -69589,7 +70420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -69855,7 +70686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -70121,7 +70952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -70387,7 +71218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -70653,7 +71484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -70919,7 +71750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -71185,7 +72016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -71451,7 +72282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -71717,7 +72548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -71983,7 +72814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -72249,7 +73080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -72515,7 +73346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -72781,7 +73612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>266</v>
       </c>
@@ -73047,7 +73878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>267</v>
       </c>
@@ -73313,7 +74144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>268</v>
       </c>
@@ -73579,7 +74410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>269</v>
       </c>
@@ -73845,7 +74676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>270</v>
       </c>
@@ -74111,7 +74942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>271</v>
       </c>
@@ -74377,7 +75208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>272</v>
       </c>
@@ -74643,7 +75474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>273</v>
       </c>
@@ -74909,7 +75740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -75175,7 +76006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>275</v>
       </c>
@@ -75441,7 +76272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>276</v>
       </c>
@@ -75707,7 +76538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -75973,7 +76804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -76239,7 +77070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>279</v>
       </c>
@@ -76505,7 +77336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -76771,7 +77602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>281</v>
       </c>
@@ -77037,7 +77868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>282</v>
       </c>
@@ -77303,7 +78134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>283</v>
       </c>
@@ -77569,7 +78400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>284</v>
       </c>
@@ -77835,7 +78666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>285</v>
       </c>
@@ -78101,7 +78932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>286</v>
       </c>
@@ -78367,7 +79198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -78633,7 +79464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -78899,7 +79730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -79165,7 +79996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -79431,7 +80262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -79697,7 +80528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -79963,7 +80794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>293</v>
       </c>
@@ -80229,7 +81060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>294</v>
       </c>
@@ -80495,7 +81326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>295</v>
       </c>
@@ -80761,7 +81592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -81027,7 +81858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>297</v>
       </c>
@@ -81293,7 +82124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>298</v>
       </c>
@@ -81559,7 +82390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -81825,7 +82656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>300</v>
       </c>
@@ -82091,7 +82922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>301</v>
       </c>
@@ -82357,7 +83188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -82623,7 +83454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -82889,7 +83720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>304</v>
       </c>
@@ -83155,7 +83986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -83430,44 +84261,44 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D28B3ADC-61CB-411C-AAF8-6DF2D6B49704}">
   <dimension ref="A1:I306"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="6" width="9.140625" style="5"/>
-    <col min="7" max="7" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="5"/>
-    <col min="9" max="9" width="13.85546875" customWidth="1"/>
+    <col min="2" max="6" width="9.109375" style="5"/>
+    <col min="7" max="7" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" style="5"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" t="s">
         <v>98</v>
       </c>
-      <c r="I1" t="s">
-        <v>99</v>
-      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -83496,7 +84327,7 @@
         <v>1.1395160900000001</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -83525,7 +84356,7 @@
         <v>1.78508245</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -83554,7 +84385,7 @@
         <v>1.31915684</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -83583,7 +84414,7 @@
         <v>1.7060643900000001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -83612,7 +84443,7 @@
         <v>1.49138226</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -83641,7 +84472,7 @@
         <v>2.0287110300000002</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -83670,7 +84501,7 @@
         <v>1.8473864499999999</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -83699,7 +84530,7 @@
         <v>1.38146722</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -83728,7 +84559,7 @@
         <v>1.6786603</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -83757,7 +84588,7 @@
         <v>1.4748592899999999</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -83786,7 +84617,7 @@
         <v>1.1642721</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -83815,7 +84646,7 @@
         <v>1.95890816</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -83844,7 +84675,7 @@
         <v>1.70334388</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -83873,7 +84704,7 @@
         <v>0.34774368</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -83902,7 +84733,7 @@
         <v>0.64717170000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -83931,7 +84762,7 @@
         <v>1.2673044499999999</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -83960,7 +84791,7 @@
         <v>0.50056573999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -83989,7 +84820,7 @@
         <v>2.4426494600000002</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -84018,7 +84849,7 @@
         <v>0.65806977</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -84047,7 +84878,7 @@
         <v>1.1127329399999999</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -84076,7 +84907,7 @@
         <v>0.99133914999999995</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -84105,7 +84936,7 @@
         <v>1.4564457200000001</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -84134,7 +84965,7 @@
         <v>1.76506045</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -84163,7 +84994,7 @@
         <v>1.7888278099999999</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -84192,7 +85023,7 @@
         <v>1.6064684899999999</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -84221,7 +85052,7 @@
         <v>1.7491939599999999</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -84250,7 +85081,7 @@
         <v>2.07428379</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -84279,7 +85110,7 @@
         <v>1.7923128800000001</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -84308,7 +85139,7 @@
         <v>2.0313234200000001</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -84337,7 +85168,7 @@
         <v>1.8838909500000001</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -84366,7 +85197,7 @@
         <v>2.0031347300000002</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -84395,7 +85226,7 @@
         <v>0.44662675000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -84424,7 +85255,7 @@
         <v>0.98088702999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -84453,7 +85284,7 @@
         <v>1.6428620700000001</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -84482,7 +85313,7 @@
         <v>0.33480617000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -84511,7 +85342,7 @@
         <v>2.3931156200000001</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -84540,7 +85371,7 @@
         <v>1.6241146099999999</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -84569,7 +85400,7 @@
         <v>1.56227385</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -84598,7 +85429,7 @@
         <v>1.35289364</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -84627,7 +85458,7 @@
         <v>1.69986712</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -84656,7 +85487,7 @@
         <v>1.3766968900000001</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -84685,7 +85516,7 @@
         <v>1.7119840900000001</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -84714,7 +85545,7 @@
         <v>1.7671074899999999</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -84743,7 +85574,7 @@
         <v>1.8075473799999999</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -84772,7 +85603,7 @@
         <v>1.70686125</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -84801,7 +85632,7 @@
         <v>1.6815542999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -84830,7 +85661,7 @@
         <v>1.79500587</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -84859,7 +85690,7 @@
         <v>1.6460838900000001</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -84888,7 +85719,7 @@
         <v>1.08663669</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -84917,7 +85748,7 @@
         <v>1.1809080999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -84946,7 +85777,7 @@
         <v>1.26952935</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -84975,7 +85806,7 @@
         <v>1.48684262</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -85004,7 +85835,7 @@
         <v>0.57772210999999996</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -85033,7 +85864,7 @@
         <v>1.70243473</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -85062,7 +85893,7 @@
         <v>0.52209905000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -85091,7 +85922,7 @@
         <v>0.23872209999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -85120,7 +85951,7 @@
         <v>0.27179881</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -85149,7 +85980,7 @@
         <v>1.7831913399999999</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -85178,7 +86009,7 @@
         <v>0.97065245</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -85207,7 +86038,7 @@
         <v>1.4316262500000001</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -85236,7 +86067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -85265,7 +86096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -85294,7 +86125,7 @@
         <v>1.1835397700000001</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -85323,7 +86154,7 @@
         <v>1.0748435199999999</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -85352,7 +86183,7 @@
         <v>1.6499258000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -85381,7 +86212,7 @@
         <v>0.53718116999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -85410,7 +86241,7 @@
         <v>0.75368541</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -85439,7 +86270,7 @@
         <v>7.0696609999999993E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -85468,7 +86299,7 @@
         <v>1.01793888</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -85497,7 +86328,7 @@
         <v>1.46030942</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -85526,7 +86357,7 @@
         <v>0.41635782999999998</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -85555,7 +86386,7 @@
         <v>1.67044237</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -85584,7 +86415,7 @@
         <v>2.4840522900000002</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -85613,7 +86444,7 @@
         <v>2.3230552100000001</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -85642,7 +86473,7 @@
         <v>1.82856018</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -85671,7 +86502,7 @@
         <v>2.1331318700000002</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -85700,7 +86531,7 @@
         <v>1.47924184</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -85729,7 +86560,7 @@
         <v>2.6027346800000002</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -85758,7 +86589,7 @@
         <v>1.6896959899999999</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -85787,7 +86618,7 @@
         <v>1.62418755</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -85816,7 +86647,7 @@
         <v>1.7830879399999999</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -85845,7 +86676,7 @@
         <v>1.9331900500000001</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -85874,7 +86705,7 @@
         <v>2.0847444300000002</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -85903,7 +86734,7 @@
         <v>2.4011659600000002</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -85932,7 +86763,7 @@
         <v>1.89092773</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -85961,7 +86792,7 @@
         <v>0.62494400999999999</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -85990,7 +86821,7 @@
         <v>1.0037607</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -86019,7 +86850,7 @@
         <v>1.45114239</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -86048,7 +86879,7 @@
         <v>0.85171158999999996</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -86077,7 +86908,7 @@
         <v>2.2665056899999998</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -86094,7 +86925,7 @@
         <v>527</v>
       </c>
       <c r="F92" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G92" s="5">
         <v>-0.80115259999999999</v>
@@ -86106,7 +86937,7 @@
         <v>1.6320117700000001</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -86123,7 +86954,7 @@
         <v>527</v>
       </c>
       <c r="F93" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G93" s="5">
         <v>-0.80115259999999999</v>
@@ -86135,7 +86966,7 @@
         <v>1.19610729</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -86164,7 +86995,7 @@
         <v>1.7705809299999999</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -86193,7 +87024,7 @@
         <v>1.8049939699999999</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -86222,7 +87053,7 @@
         <v>1.6177431499999999</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -86251,7 +87082,7 @@
         <v>1.4145975399999999</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -86280,7 +87111,7 @@
         <v>1.67760216</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -86309,7 +87140,7 @@
         <v>1.2020639</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -86338,7 +87169,7 @@
         <v>1.76760235</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -86367,7 +87198,7 @@
         <v>1.4722392099999999</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -86396,7 +87227,7 @@
         <v>1.9521303400000001</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -86425,7 +87256,7 @@
         <v>1.7528096399999999</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -86454,7 +87285,7 @@
         <v>1.36192183</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -86483,7 +87314,7 @@
         <v>0.90085110000000002</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -86512,7 +87343,7 @@
         <v>1.0105177299999999</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -86541,7 +87372,7 @@
         <v>0.70986674999999999</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -86570,7 +87401,7 @@
         <v>0.99200504</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -86599,7 +87430,7 @@
         <v>1.9142851000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -86628,7 +87459,7 @@
         <v>0.45772326000000002</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -86657,7 +87488,7 @@
         <v>2.4491405400000001</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -86674,7 +87505,7 @@
         <v>568</v>
       </c>
       <c r="F112" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G112" s="5">
         <v>-0.80115259999999999</v>
@@ -86686,7 +87517,7 @@
         <v>1.92991139</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -86703,7 +87534,7 @@
         <v>568</v>
       </c>
       <c r="F113" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G113" s="5">
         <v>-0.80115259999999999</v>
@@ -86715,7 +87546,7 @@
         <v>1.8733360800000001</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -86744,7 +87575,7 @@
         <v>1.27904617</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -86773,7 +87604,7 @@
         <v>1.3826604600000001</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -86802,7 +87633,7 @@
         <v>1.5639474600000001</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -86831,7 +87662,7 @@
         <v>1.4194650200000001</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -86860,7 +87691,7 @@
         <v>1.1651975000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -86889,7 +87720,7 @@
         <v>0.81631741999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -86918,7 +87749,7 @@
         <v>1.1062745700000001</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -86947,7 +87778,7 @@
         <v>1.77088376</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -86976,7 +87807,7 @@
         <v>2.0660956700000002</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -87005,7 +87836,7 @@
         <v>1.5441607399999999</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -87034,7 +87865,7 @@
         <v>1.5604093999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -87063,7 +87894,7 @@
         <v>0.54231976999999998</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -87092,7 +87923,7 @@
         <v>0.85273761999999997</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -87121,7 +87952,7 @@
         <v>1.6004913199999999</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -87150,7 +87981,7 @@
         <v>1.6736028700000001</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -87179,7 +88010,7 @@
         <v>1.8899544100000001</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -87208,7 +88039,7 @@
         <v>0.36501940999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -87237,7 +88068,7 @@
         <v>1.1799027099999999</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -87254,7 +88085,7 @@
         <v>609</v>
       </c>
       <c r="F132" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G132" s="5">
         <v>-0.80115259999999999</v>
@@ -87266,7 +88097,7 @@
         <v>1.6014885800000001</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -87283,7 +88114,7 @@
         <v>609</v>
       </c>
       <c r="F133" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G133" s="5">
         <v>-0.80115259999999999</v>
@@ -87295,7 +88126,7 @@
         <v>1.0969308900000001</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -87324,7 +88155,7 @@
         <v>0.14487807</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -87353,7 +88184,7 @@
         <v>0.31177881000000002</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -87382,7 +88213,7 @@
         <v>0.49476659000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -87411,7 +88242,7 @@
         <v>1.7752487299999999</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -87440,7 +88271,7 @@
         <v>1.519593</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -87469,7 +88300,7 @@
         <v>1.7112386399999999</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -87498,7 +88329,7 @@
         <v>0.41092578000000002</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -87527,7 +88358,7 @@
         <v>1.43228833</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -87556,7 +88387,7 @@
         <v>0.82698716999999999</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -87585,7 +88416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -87614,7 +88445,7 @@
         <v>1.3646575000000001</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -87643,7 +88474,7 @@
         <v>0.52168028</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -87672,7 +88503,7 @@
         <v>0.63604704999999995</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -87701,7 +88532,7 @@
         <v>1.0636474499999999</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -87730,7 +88561,7 @@
         <v>7.1012220000000001E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -87759,7 +88590,7 @@
         <v>1.11952995</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -87788,7 +88619,7 @@
         <v>0.14120704000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -87817,7 +88648,7 @@
         <v>1.63025771</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -87834,7 +88665,7 @@
         <v>659</v>
       </c>
       <c r="F152" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G152" s="5">
         <v>-0.80115259999999999</v>
@@ -87846,7 +88677,7 @@
         <v>2.2585079399999999</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -87863,7 +88694,7 @@
         <v>659</v>
       </c>
       <c r="F153" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G153" s="5">
         <v>-0.80115259999999999</v>
@@ -87875,7 +88706,7 @@
         <v>2.2852496000000002</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -87904,7 +88735,7 @@
         <v>0.86730971000000001</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -87933,7 +88764,7 @@
         <v>1.60690661</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -87962,7 +88793,7 @@
         <v>0.83329427</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -87991,7 +88822,7 @@
         <v>1.9389763600000001</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -88020,7 +88851,7 @@
         <v>1.48570541</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -88049,7 +88880,7 @@
         <v>2.0236097900000001</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -88078,7 +88909,7 @@
         <v>1.5328693600000001</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -88107,7 +88938,7 @@
         <v>1.7654068199999999</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -88136,7 +88967,7 @@
         <v>1.2010794</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -88165,7 +88996,7 @@
         <v>1.7558158399999999</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -88194,7 +89025,7 @@
         <v>2.0471740199999999</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -88223,7 +89054,7 @@
         <v>1.9053784899999999</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -88252,7 +89083,7 @@
         <v>1.83827005</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -88281,7 +89112,7 @@
         <v>0.33097686999999998</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -88310,7 +89141,7 @@
         <v>1.1209334</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -88339,7 +89170,7 @@
         <v>1.01588455</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -88368,7 +89199,7 @@
         <v>0.56865379999999999</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -88397,7 +89228,7 @@
         <v>1.0330321600000001</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -88414,7 +89245,7 @@
         <v>890</v>
       </c>
       <c r="F172" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G172" s="5">
         <v>-0.80115259999999999</v>
@@ -88426,7 +89257,7 @@
         <v>2.2641640000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -88443,7 +89274,7 @@
         <v>890</v>
       </c>
       <c r="F173" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G173" s="5">
         <v>-0.80115259999999999</v>
@@ -88455,7 +89286,7 @@
         <v>2.1345999999999998</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -88484,7 +89315,7 @@
         <v>1.37818186</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -88513,7 +89344,7 @@
         <v>1.2004723500000001</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -88542,7 +89373,7 @@
         <v>0.83148363000000003</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -88571,7 +89402,7 @@
         <v>1.4112252199999999</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -88600,7 +89431,7 @@
         <v>1.6303742699999999</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -88629,7 +89460,7 @@
         <v>0.93075169999999996</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -88658,7 +89489,7 @@
         <v>1.5902593700000001</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -88687,7 +89518,7 @@
         <v>1.74629378</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -88716,7 +89547,7 @@
         <v>0.58654214999999998</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -88745,7 +89576,7 @@
         <v>1.50589934</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -88774,7 +89605,7 @@
         <v>1.8835478699999999</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -88803,7 +89634,7 @@
         <v>1.6301569600000001</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -88832,7 +89663,7 @@
         <v>1.1027005299999999</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -88861,7 +89692,7 @@
         <v>0.52356168000000003</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -88890,7 +89721,7 @@
         <v>1.24505994</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -88919,7 +89750,7 @@
         <v>1.71610303</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -88948,7 +89779,7 @@
         <v>0.58464119000000003</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -88977,7 +89808,7 @@
         <v>2.3006363300000001</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -88994,7 +89825,7 @@
         <v>930</v>
       </c>
       <c r="F192" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G192" s="5">
         <v>-0.80115259999999999</v>
@@ -89006,7 +89837,7 @@
         <v>1.4288336800000001</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -89023,7 +89854,7 @@
         <v>930</v>
       </c>
       <c r="F193" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G193" s="5">
         <v>-0.80115259999999999</v>
@@ -89035,7 +89866,7 @@
         <v>1.5748640599999999</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -89064,7 +89895,7 @@
         <v>0.90384748999999998</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -89093,7 +89924,7 @@
         <v>0.69839001999999994</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -89122,7 +89953,7 @@
         <v>1.41621587</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -89151,7 +89982,7 @@
         <v>1.76444801</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -89180,7 +90011,7 @@
         <v>1.3124489500000001</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -89209,7 +90040,7 @@
         <v>1.4070476000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -89238,7 +90069,7 @@
         <v>0.96146220999999998</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -89267,7 +90098,7 @@
         <v>1.6464895500000001</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -89296,7 +90127,7 @@
         <v>1.6887400299999999</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -89325,7 +90156,7 @@
         <v>1.0778233800000001</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -89354,7 +90185,7 @@
         <v>1.8752500999999999</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -89383,7 +90214,7 @@
         <v>1.2076200800000001</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -89412,7 +90243,7 @@
         <v>0.64633335000000003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -89441,7 +90272,7 @@
         <v>1.1203483700000001</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -89470,7 +90301,7 @@
         <v>1.0895326599999999</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -89499,7 +90330,7 @@
         <v>1.51029795</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -89528,7 +90359,7 @@
         <v>0.48405532000000001</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -89557,7 +90388,7 @@
         <v>0.58531648000000003</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -89574,7 +90405,7 @@
         <v>977</v>
       </c>
       <c r="F212" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G212" s="5">
         <v>-0.80115259999999999</v>
@@ -89586,7 +90417,7 @@
         <v>0.98923903000000002</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -89603,7 +90434,7 @@
         <v>977</v>
       </c>
       <c r="F213" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G213" s="5">
         <v>-0.80115259999999999</v>
@@ -89615,7 +90446,7 @@
         <v>1.5508414399999999</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -89644,7 +90475,7 @@
         <v>0.84765988999999997</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -89673,7 +90504,7 @@
         <v>0.15788938</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -89702,7 +90533,7 @@
         <v>0.39497658000000002</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -89731,7 +90562,7 @@
         <v>0.98265309999999995</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -89760,7 +90591,7 @@
         <v>1.04816278</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -89789,7 +90620,7 @@
         <v>1.42492686</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -89818,7 +90649,7 @@
         <v>0.62439445999999998</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -89847,7 +90678,7 @@
         <v>1.4062978900000001</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -89876,7 +90707,7 @@
         <v>0.49208987999999998</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -89905,7 +90736,7 @@
         <v>1.6662835499999999</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -89934,7 +90765,7 @@
         <v>1.6436659300000001</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -89963,7 +90794,7 @@
         <v>0.37794952999999998</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -89992,7 +90823,7 @@
         <v>0.37769593000000001</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -90021,7 +90852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -90050,7 +90881,7 @@
         <v>0.36783484</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -90079,7 +90910,7 @@
         <v>1.6676744699999999</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -90108,7 +90939,7 @@
         <v>0.43751171999999999</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -90137,7 +90968,7 @@
         <v>2.0175737699999998</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -90154,7 +90985,7 @@
         <v>1029</v>
       </c>
       <c r="F232" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G232" s="5">
         <v>-0.80115259999999999</v>
@@ -90166,7 +90997,7 @@
         <v>0.82419872999999999</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -90183,7 +91014,7 @@
         <v>1029</v>
       </c>
       <c r="F233" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G233" s="5">
         <v>-0.80115259999999999</v>
@@ -90195,7 +91026,7 @@
         <v>2.1519200000000001</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -90224,7 +91055,7 @@
         <v>2.1141286699999999</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -90253,7 +91084,7 @@
         <v>2.2369543200000002</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -90282,7 +91113,7 @@
         <v>2.05301811</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -90311,7 +91142,7 @@
         <v>1.8262086900000001</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -90340,7 +91171,7 @@
         <v>1.64261977</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -90369,7 +91200,7 @@
         <v>2.20932241</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -90398,7 +91229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -90427,7 +91258,7 @@
         <v>2.1213674</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -90456,7 +91287,7 @@
         <v>0.74695884000000001</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -90485,7 +91316,7 @@
         <v>1.45791125</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -90514,7 +91345,7 @@
         <v>1.6293114500000001</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -90543,7 +91374,7 @@
         <v>1.7493881</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -90572,7 +91403,7 @@
         <v>1.66782169</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -90601,7 +91432,7 @@
         <v>0.71673606999999995</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -90630,7 +91461,7 @@
         <v>1.7602946100000001</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -90659,7 +91490,7 @@
         <v>0.76073681999999998</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>249</v>
       </c>
@@ -90688,7 +91519,7 @@
         <v>0.68150979</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -90705,7 +91536,7 @@
         <v>1258</v>
       </c>
       <c r="F251" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G251" s="5">
         <v>-0.80115259999999999</v>
@@ -90717,7 +91548,7 @@
         <v>1.84264709</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -90734,7 +91565,7 @@
         <v>1258</v>
       </c>
       <c r="F252" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G252" s="5">
         <v>-0.80115259999999999</v>
@@ -90746,7 +91577,7 @@
         <v>1.8085070599999999</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -90775,7 +91606,7 @@
         <v>1.3669289499999999</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -90804,7 +91635,7 @@
         <v>0.72210293999999997</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -90833,7 +91664,7 @@
         <v>0.52844347999999997</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -90862,7 +91693,7 @@
         <v>1.8910069300000001</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -90891,7 +91722,7 @@
         <v>1.8755406800000001</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -90920,7 +91751,7 @@
         <v>1.2358966600000001</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -90949,7 +91780,7 @@
         <v>1.69644025</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -90978,7 +91809,7 @@
         <v>0.81616781000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -91007,7 +91838,7 @@
         <v>1.6202567299999999</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -91036,7 +91867,7 @@
         <v>1.75381776</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -91065,7 +91896,7 @@
         <v>1.6297378</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -91094,7 +91925,7 @@
         <v>1.49705244</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -91123,7 +91954,7 @@
         <v>0.51699410000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -91152,7 +91983,7 @@
         <v>1.3854505399999999</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>266</v>
       </c>
@@ -91181,7 +92012,7 @@
         <v>1.76067755</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>267</v>
       </c>
@@ -91210,7 +92041,7 @@
         <v>0.66582105000000003</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>268</v>
       </c>
@@ -91239,7 +92070,7 @@
         <v>1.9046454900000001</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>269</v>
       </c>
@@ -91256,7 +92087,7 @@
         <v>1303</v>
       </c>
       <c r="F270" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G270" s="5">
         <v>-0.80115259999999999</v>
@@ -91268,7 +92099,7 @@
         <v>0.81487191000000003</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>270</v>
       </c>
@@ -91285,7 +92116,7 @@
         <v>1303</v>
       </c>
       <c r="F271" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G271" s="5">
         <v>-0.80115259999999999</v>
@@ -91297,7 +92128,7 @@
         <v>1.5249822500000001</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>271</v>
       </c>
@@ -91326,7 +92157,7 @@
         <v>0.41523199999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>272</v>
       </c>
@@ -91355,7 +92186,7 @@
         <v>0.55310408</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>273</v>
       </c>
@@ -91384,7 +92215,7 @@
         <v>0.84443126999999996</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -91413,7 +92244,7 @@
         <v>1.16060662</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>275</v>
       </c>
@@ -91442,7 +92273,7 @@
         <v>1.4204147</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>276</v>
       </c>
@@ -91471,7 +92302,7 @@
         <v>1.3915497699999999</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -91500,7 +92331,7 @@
         <v>1.5262344299999999</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -91529,7 +92360,7 @@
         <v>1.4656672500000001</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>279</v>
       </c>
@@ -91558,7 +92389,7 @@
         <v>1.7139296399999999</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -91587,7 +92418,7 @@
         <v>0.55039066999999997</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>281</v>
       </c>
@@ -91616,7 +92447,7 @@
         <v>0.65040050000000005</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>282</v>
       </c>
@@ -91645,7 +92476,7 @@
         <v>0.15903308999999999</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>283</v>
       </c>
@@ -91674,7 +92505,7 @@
         <v>1.6170908900000001</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>284</v>
       </c>
@@ -91703,7 +92534,7 @@
         <v>1.88226413</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>285</v>
       </c>
@@ -91732,7 +92563,7 @@
         <v>0.63283180000000006</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>286</v>
       </c>
@@ -91761,7 +92592,7 @@
         <v>0.74849631000000005</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -91778,7 +92609,7 @@
         <v>1345</v>
       </c>
       <c r="F288" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G288" s="5">
         <v>-0.80115259999999999</v>
@@ -91790,7 +92621,7 @@
         <v>1.00131397</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -91807,7 +92638,7 @@
         <v>1345</v>
       </c>
       <c r="F289" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G289" s="5">
         <v>-0.80115259999999999</v>
@@ -91819,7 +92650,7 @@
         <v>1.3641925800000001</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -91848,7 +92679,7 @@
         <v>0.57296533999999999</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -91877,7 +92708,7 @@
         <v>0.19956979999999999</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -91906,7 +92737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -91935,7 +92766,7 @@
         <v>0.83510614000000005</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>293</v>
       </c>
@@ -91964,7 +92795,7 @@
         <v>1.32217183</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>294</v>
       </c>
@@ -91993,7 +92824,7 @@
         <v>0.28813984999999998</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>295</v>
       </c>
@@ -92022,7 +92853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -92051,7 +92882,7 @@
         <v>1.58352176</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>297</v>
       </c>
@@ -92080,7 +92911,7 @@
         <v>8.8672899999999999E-3</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>298</v>
       </c>
@@ -92109,7 +92940,7 @@
         <v>1.6319130000000001E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -92138,7 +92969,7 @@
         <v>0.22093525</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>300</v>
       </c>
@@ -92167,7 +92998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>301</v>
       </c>
@@ -92196,7 +93027,7 @@
         <v>1.0556993100000001</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -92225,7 +93056,7 @@
         <v>1.68020462</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -92254,7 +93085,7 @@
         <v>0.40920358000000001</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>304</v>
       </c>
@@ -92271,7 +93102,7 @@
         <v>1393</v>
       </c>
       <c r="F305" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G305" s="5">
         <v>-0.80115259999999999</v>
@@ -92283,7 +93114,7 @@
         <v>0.54692258999999999</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -92300,7 +93131,7 @@
         <v>1393</v>
       </c>
       <c r="F306" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G306" s="5">
         <v>-0.80115259999999999</v>
